--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3299-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3299-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B2D611F-F1E0-4C48-82A2-2BBE5BB6CBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E0CF855-78B0-4772-9C61-0CA7C3D9A655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{74AEABB4-9F6A-40A0-8641-204C91D0867D}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{B5D65607-1465-4E82-AEF8-C58E407EB275}"/>
   </bookViews>
   <sheets>
     <sheet name="3299-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1451,27 +1451,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0410FE-7A60-4E75-8FFB-A2FD6088FE3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA9D50C9-2F01-43BB-B9B3-9EE9D7CE038B}">
   <dimension ref="A1:X21"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="6.25" customWidth="1"/>
-    <col min="15" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1505,7 +1504,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1541,7 +1540,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1593,7 +1592,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1661,7 +1660,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2017</v>
       </c>
@@ -1733,7 +1732,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2016</v>
       </c>
@@ -1805,7 +1804,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2015</v>
       </c>
@@ -1877,7 +1876,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2014</v>
       </c>
@@ -1949,7 +1948,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2013</v>
       </c>
@@ -2021,7 +2020,7 @@
         <v>9.33</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2012</v>
       </c>
@@ -2093,7 +2092,7 @@
         <v>8.98</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2011</v>
       </c>
@@ -2165,7 +2164,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2010</v>
       </c>
@@ -2237,7 +2236,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2009</v>
       </c>
@@ -2309,7 +2308,7 @@
         <v>7.67</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2008</v>
       </c>
@@ -2381,7 +2380,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2007</v>
       </c>
@@ -2453,7 +2452,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2006</v>
       </c>
@@ -2525,7 +2524,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2005</v>
       </c>
@@ -2597,7 +2596,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2004</v>
       </c>
@@ -2669,7 +2668,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2003</v>
       </c>
@@ -2741,7 +2740,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2002</v>
       </c>
@@ -2813,7 +2812,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33" t="s">
         <v>43</v>
       </c>
